--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109495405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109498196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,57 +798,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109498196</v>
+        <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>111129</v>
+        <v>99299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221049</v>
+        <v>219799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sävedal, 300 m NV. Vid NO-delen av Väjla sjö, Sk</t>
+          <t>Väla Sjö, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460388</v>
+        <v>460333</v>
       </c>
       <c r="R3" t="n">
-        <v>6212721</v>
+        <v>6212618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +877,14 @@
           <t>Kiaby</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Kri-0099</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,28 +897,148 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136337803</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109498196</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sävedal, 300 m NV. Vid NO-delen av Väjla sjö, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>460388</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6212721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Kri-0099</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Gunnar Svensson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109498196</t>
         </is>
@@ -929,6 +1048,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99299</v>
+        <v>99312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99312</v>
+        <v>99313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99313</v>
+        <v>99326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
